--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.175.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.175.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.175" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.175" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,19 +581,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.175.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.175.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0175.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>L48: possible duplicated/overlap line with previous line (similarity 66%) :: 9. At page 104, in the first paragraph, for " the hearing appointment, read</t>
-        </is>
-      </c>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0175.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -786,7 +782,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -899,12 +895,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.175.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.175.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.175" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.175" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,22 +422,22 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -603,18 +603,18 @@
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUBPENA â€” Continued.</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUBPNA-â€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]168</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]168</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 168</t>
@@ -622,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L34: symbol-only separator/garbage line :: % ___________________________-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]168</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -632,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 51</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,14 +674,10 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Form of Subp Ã¦ na issued by Master, to add parties</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: VACATION ..............................â€¢</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: VACATION ..............................•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L36: symbol-only separator/garbage line :: .49</t>
+          <t>L34: symbol-only separator/garbage line :: % ___________________________-</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -737,14 +737,10 @@
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œthe appointment and for constitutes appointments, read " constitutes the</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 51</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 51</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -756,7 +752,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 139</t>
+          <t>L36: symbol-only separator/garbage line :: .49</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -782,12 +778,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -801,11 +797,7 @@
       </c>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1. At page 5, the first line should read â€œis said to deal with it" &amp;c., instead of</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -815,7 +807,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L40: symbol-only separator/garbage line :: .16</t>
+          <t>L38: isolated marker/symbol line :: 139</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -860,11 +852,7 @@
       </c>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: repeated periods :: Â«dealsâ€� &amp;c..</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -874,7 +862,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L42: symbol-only separator/garbage line :: .15</t>
+          <t>L40: symbol-only separator/garbage line :: .16</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -925,13 +913,13 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L46: symbol-only separator/garbage line :: . 51</t>
+          <t>L42: symbol-only separator/garbage line :: .15</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: VACATION ..............................â€¢</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: VACATION ..............................•</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -976,13 +964,13 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L48: symbol-only separator/garbage line :: - 52</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 51</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | punctuation artifact: repeated periods :: Â«dealsâ€� &amp;c..</t>
+          <t>L59: punctuation artifact: repeated periods :: «deals” &amp;c..</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1027,13 +1015,13 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L50: symbol-only separator/garbage line :: .52</t>
+          <t>L46: symbol-only separator/garbage line :: . 51</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L66: punctuation artifact: repeated periods :: instead of Â« all applications for leave" &amp;c..</t>
+          <t>L66: punctuation artifact: repeated periods :: instead of « all applications for leave" &amp;c..</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1053,12 +1041,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1078,7 +1066,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 106</t>
+          <t>L48: symbol-only separator/garbage line :: - 52</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1109,7 +1097,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1129,7 +1117,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: N</t>
+          <t>L50: symbol-only separator/garbage line :: .52</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1156,7 +1144,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1176,7 +1164,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: a</t>
+          <t>L52: isolated marker/symbol line :: 106</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1217,7 +1205,11 @@
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr"/>
-      <c r="O13" s="1" t="inlineStr"/>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>L90: isolated marker/symbol line :: N</t>
+        </is>
+      </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr"/>
@@ -1242,7 +1234,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1256,7 +1248,11 @@
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr"/>
-      <c r="O14" s="1" t="inlineStr"/>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>L92: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
